--- a/data/trans_camb/P16A15-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Edad-trans_camb.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,49</t>
+          <t>0,3; 2,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,04</t>
+          <t>-0,33; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,07</t>
+          <t>-0,41; 1,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,8</t>
+          <t>-0,13; 1,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,35</t>
+          <t>-0,61; 0,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,82</t>
+          <t>-0,26; 1,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,9</t>
+          <t>0,32; 1,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,46</t>
+          <t>-0,35; 0,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,03</t>
+          <t>-0,17; 1,01</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,15; —</t>
+          <t>-20,71; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,04; 1727,04</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-84,32; 635,42</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,2; 1594,38</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-82,21; 564,2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-64,02; 934,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,22</t>
+          <t>-0,72; 3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,47</t>
+          <t>-1,35; 2,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,74</t>
+          <t>-1,09; 2,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,33</t>
+          <t>-1,02; 2,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,06</t>
+          <t>-2,46; 0,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,1</t>
+          <t>-2,52; 0,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,21</t>
+          <t>-0,34; 2,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,83</t>
+          <t>-1,32; 0,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,89</t>
+          <t>-1,27; 0,98</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 203,86</t>
+          <t>-26,7; 200,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 178,38</t>
+          <t>-43,18; 158,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 180,92</t>
+          <t>-38,4; 165,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 193,17</t>
+          <t>-39,74; 178,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,73; 16,95</t>
+          <t>-86,55; 19,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,66; 20,33</t>
+          <t>-82,58; 14,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 139,46</t>
+          <t>-13,56; 140,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 52,13</t>
+          <t>-50,64; 51,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 55,03</t>
+          <t>-48,17; 62,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,61</t>
+          <t>-0,61; 5,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,05</t>
+          <t>-0,94; 5,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,22</t>
+          <t>-3,32; 5,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,17</t>
+          <t>1,12; 7,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,05</t>
+          <t>0,24; 5,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,26</t>
+          <t>-1,42; 3,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,53</t>
+          <t>1,15; 5,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,54</t>
+          <t>0,4; 4,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,05</t>
+          <t>-1,67; 3,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 138,25</t>
+          <t>-9,64; 132,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 123,83</t>
+          <t>-14,49; 119,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 107,66</t>
+          <t>-48,81; 108,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,85; 201,23</t>
+          <t>16,0; 213,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 173,24</t>
+          <t>1,92; 164,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 90,6</t>
+          <t>-23,75; 98,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,51; 130,33</t>
+          <t>15,59; 126,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,77; 101,15</t>
+          <t>6,13; 100,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 67,72</t>
+          <t>-27,01; 77,6</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 11,9</t>
+          <t>0,19; 11,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 7,07</t>
+          <t>-2,54; 7,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,96</t>
+          <t>1,59; 10,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 13,81</t>
+          <t>1,92; 13,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 10,29</t>
+          <t>0,3; 10,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 10,08</t>
+          <t>1,21; 9,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,81</t>
+          <t>3,22; 10,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 7,27</t>
+          <t>-0,11; 7,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,16</t>
+          <t>2,77; 9,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,1; 101,68</t>
+          <t>0,76; 98,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 63,04</t>
+          <t>-15,84; 67,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,94; 100,53</t>
+          <t>9,19; 96,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,3; 113,85</t>
+          <t>10,21; 102,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 80,88</t>
+          <t>1,62; 81,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,64; 80,47</t>
+          <t>5,71; 80,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,16; 87,77</t>
+          <t>18,8; 85,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,74; 58,75</t>
+          <t>-0,57; 55,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17,3; 74,74</t>
+          <t>16,85; 78,77</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,74; 24,08</t>
+          <t>9,83; 24,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,84; 18,44</t>
+          <t>5,15; 18,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,47; 15,84</t>
+          <t>5,21; 16,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,27; 14,72</t>
+          <t>1,09; 14,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 9,84</t>
+          <t>-2,51; 9,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,03; 56,93</t>
+          <t>5,47; 55,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,22; 17,35</t>
+          <t>6,66; 17,01</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,11; 12,14</t>
+          <t>2,64; 11,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,65; 48,96</t>
+          <t>7,68; 49,6</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>45,23; 164,71</t>
+          <t>45,24; 164,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23,56; 124,41</t>
+          <t>24,24; 125,65</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20,45; 109,65</t>
+          <t>26,26; 121,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4,09; 68,37</t>
+          <t>3,77; 65,74</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 44,68</t>
+          <t>-9,31; 46,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,45; 266,32</t>
+          <t>20,74; 266,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,81; 90,06</t>
+          <t>28,27; 88,34</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>13,16; 62,42</t>
+          <t>11,5; 61,35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>34,01; 272,87</t>
+          <t>33,48; 244,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,44; 20,44</t>
+          <t>3,51; 21,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,56; 16,91</t>
+          <t>2,21; 17,26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,45; 22,74</t>
+          <t>9,4; 23,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,97; 18,15</t>
+          <t>4,66; 18,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 14,44</t>
+          <t>-0,39; 14,02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,75; 23,91</t>
+          <t>11,57; 23,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,14; 16,94</t>
+          <t>6,56; 17,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,72; 13,65</t>
+          <t>3,0; 13,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,73; 21,53</t>
+          <t>12,35; 21,23</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18,74; 136,55</t>
+          <t>12,72; 138,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6,11; 112,57</t>
+          <t>8,81; 118,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,79; 148,69</t>
+          <t>38,89; 158,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,46; 87,94</t>
+          <t>15,6; 87,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,22; 71,74</t>
+          <t>-1,48; 70,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,12; 120,83</t>
+          <t>40,5; 115,55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,35; 86,83</t>
+          <t>26,32; 88,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>10,46; 70,03</t>
+          <t>12,67; 71,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50,07; 111,74</t>
+          <t>47,77; 110,84</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,76</t>
+          <t>3,22; 5,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,85</t>
+          <t>2,31; 4,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,25</t>
+          <t>2,3; 7,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,75</t>
+          <t>2,93; 5,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,57</t>
+          <t>1,68; 4,5</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,5; 26,72</t>
+          <t>5,36; 23,95</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,45</t>
+          <t>3,34; 5,37</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,39</t>
+          <t>2,41; 4,38</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,37; 17,71</t>
+          <t>5,29; 17,69</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>47,88; 110,72</t>
+          <t>50,08; 111,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>36,33; 92,83</t>
+          <t>35,68; 95,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>56,76; 137,98</t>
+          <t>41,41; 133,74</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32,37; 78,8</t>
+          <t>34,92; 82,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,12; 62,36</t>
+          <t>19,17; 62,35</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>68,62; 347,52</t>
+          <t>65,32; 308,96</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,58; 83,89</t>
+          <t>46,5; 84,27</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>31,85; 67,24</t>
+          <t>33,25; 68,66</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>76,44; 274,75</t>
+          <t>76,77; 271,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A15-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,41</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,67</t>
+          <t>0,29; 2,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,07</t>
+          <t>-0,35; 1,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,07</t>
+          <t>-0,41; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,88</t>
+          <t>-0,1; 1,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,35</t>
+          <t>-0,63; 0,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,56</t>
+          <t>-0,21; 1,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,91</t>
+          <t>0,36; 1,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,53</t>
+          <t>-0,33; 0,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,01</t>
+          <t>-0,18; 1,04</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>176,91%</t>
+          <t>183,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108,18%</t>
+          <t>102,72%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,71; —</t>
+          <t>-38,36; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 1727,04</t>
+          <t>43,05; 1766,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,32; 635,42</t>
+          <t>-100,0; 545,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-61,3; 924,78</t>
         </is>
       </c>
     </row>
@@ -1066,14 +1066,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,74</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,12</t>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,14</t>
+          <t>-0,75; 3,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,34</t>
+          <t>-1,32; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,75</t>
+          <t>-0,85; 3,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,26</t>
+          <t>-0,87; 2,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,03</t>
+          <t>-2,38; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,02</t>
+          <t>-2,16; 0,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,17</t>
+          <t>-0,27; 2,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,82</t>
+          <t>-1,3; 0,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,98</t>
+          <t>-1,02; 1,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-53,8%</t>
+          <t>-33,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,12%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 200,25</t>
+          <t>-26,14; 214,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 158,19</t>
+          <t>-41,18; 163,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 165,22</t>
+          <t>-30,55; 193,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 178,24</t>
+          <t>-33,62; 190,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,55; 19,69</t>
+          <t>-84,98; 20,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,58; 14,6</t>
+          <t>-71,38; 66,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 140,73</t>
+          <t>-13,37; 133,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 51,1</t>
+          <t>-50,71; 50,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 62,31</t>
+          <t>-40,07; 80,32</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,53</t>
+          <t>-0,5; 5,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,06</t>
+          <t>-0,77; 5,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 5,3</t>
+          <t>0,39; 6,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,62</t>
+          <t>1,05; 7,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,88</t>
+          <t>0,56; 5,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,27</t>
+          <t>-1,38; 3,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,64</t>
+          <t>1,09; 5,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,42</t>
+          <t>0,48; 4,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,53</t>
+          <t>0,35; 4,05</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 132,22</t>
+          <t>-10,41; 132,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 119,75</t>
+          <t>-12,31; 125,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 108,94</t>
+          <t>5,69; 156,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,0; 213,53</t>
+          <t>16,84; 206,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 164,25</t>
+          <t>6,81; 167,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 98,92</t>
+          <t>-20,4; 88,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,59; 126,8</t>
+          <t>16,38; 129,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,13; 100,69</t>
+          <t>3,97; 106,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 77,6</t>
+          <t>5,3; 97,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>5,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 11,09</t>
+          <t>0,6; 11,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,32</t>
+          <t>-3,12; 6,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 10,65</t>
+          <t>0,91; 9,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 13,05</t>
+          <t>1,86; 12,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 10,59</t>
+          <t>0,01; 10,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,98</t>
+          <t>1,01; 9,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,98</t>
+          <t>2,98; 10,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 7,07</t>
+          <t>-0,42; 7,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,41</t>
+          <t>2,06; 8,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,76; 98,56</t>
+          <t>3,3; 101,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 67,42</t>
+          <t>-20,79; 59,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,19; 96,05</t>
+          <t>4,46; 86,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,21; 102,53</t>
+          <t>10,14; 104,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,62; 81,83</t>
+          <t>-0,54; 81,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,71; 80,16</t>
+          <t>3,69; 78,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,8; 85,1</t>
+          <t>18,52; 85,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 55,44</t>
+          <t>-2,33; 57,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,85; 78,77</t>
+          <t>12,33; 67,15</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10,51</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,44</t>
+          <t>7,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23,53</t>
+          <t>8,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,83; 24,31</t>
+          <t>9,57; 24,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,15; 18,32</t>
+          <t>5,53; 18,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,21; 16,29</t>
+          <t>4,45; 16,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,09; 14,3</t>
+          <t>0,81; 14,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 9,86</t>
+          <t>-3,75; 9,57</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,47; 55,3</t>
+          <t>2,11; 12,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,66; 17,01</t>
+          <t>6,62; 16,54</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,75</t>
+          <t>2,97; 11,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,68; 49,6</t>
+          <t>4,74; 12,47</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>122,86%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>109,89%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>45,24; 164,51</t>
+          <t>46,27; 166,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24,24; 125,65</t>
+          <t>28,23; 134,42</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26,26; 121,22</t>
+          <t>19,89; 112,9</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,77; 65,74</t>
+          <t>3,56; 69,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 46,2</t>
+          <t>-13,12; 44,12</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,74; 266,16</t>
+          <t>7,47; 61,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,27; 88,34</t>
+          <t>27,98; 83,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>11,5; 61,35</t>
+          <t>13,14; 63,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33,48; 244,35</t>
+          <t>20,02; 65,88</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16,33</t>
+          <t>16,21</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,71</t>
+          <t>17,21</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,09</t>
+          <t>16,74</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,51; 21,13</t>
+          <t>4,22; 20,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,21; 17,26</t>
+          <t>1,9; 16,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,4; 23,27</t>
+          <t>8,67; 23,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,66; 18,13</t>
+          <t>4,3; 18,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 14,02</t>
+          <t>-0,4; 13,57</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,57; 23,46</t>
+          <t>11,05; 22,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,56; 17,41</t>
+          <t>6,08; 16,9</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,0; 13,57</t>
+          <t>3,03; 13,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,35; 21,23</t>
+          <t>11,94; 21,3</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,72; 138,29</t>
+          <t>18,64; 130,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8,81; 118,09</t>
+          <t>6,84; 109,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38,89; 158,58</t>
+          <t>35,22; 156,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,6; 87,92</t>
+          <t>15,23; 87,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 70,51</t>
+          <t>-1,82; 65,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,5; 115,55</t>
+          <t>38,88; 114,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,32; 88,67</t>
+          <t>23,59; 86,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>12,67; 71,79</t>
+          <t>11,52; 68,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>47,77; 110,84</t>
+          <t>46,11; 110,44</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,65</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>6,09</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,82</t>
+          <t>3,18; 5,91</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,95</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,16</t>
+          <t>4,9; 7,37</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,9</t>
+          <t>2,86; 5,77</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,5</t>
+          <t>1,64; 4,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,36; 23,95</t>
+          <t>4,74; 7,26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,37</t>
+          <t>3,52; 5,39</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,38</t>
+          <t>2,32; 4,32</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,29; 17,69</t>
+          <t>5,07; 7,02</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>106,02%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>134,93%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>119,62%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>50,08; 111,49</t>
+          <t>49,76; 112,69</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>35,68; 95,1</t>
+          <t>35,47; 90,41</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>41,41; 133,74</t>
+          <t>76,19; 143,26</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34,92; 82,3</t>
+          <t>32,68; 80,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,17; 62,35</t>
+          <t>18,33; 62,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>65,32; 308,96</t>
+          <t>55,16; 104,48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,5; 84,27</t>
+          <t>47,78; 84,04</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>33,25; 68,66</t>
+          <t>31,61; 66,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>76,77; 271,6</t>
+          <t>68,32; 109,89</t>
         </is>
       </c>
     </row>
